--- a/reports/pdf_rolling5_20260701.xlsx
+++ b/reports/pdf_rolling5_20260701.xlsx
@@ -128,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -161,6 +161,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -530,16 +536,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="3" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -568,6 +576,8 @@
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -577,13 +587,15 @@
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n"/>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="D4" s="6" t="n"/>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="F4" s="8" t="n"/>
       <c r="G4" s="8" t="n"/>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -593,25 +605,35 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>변화</t>
+          <t>변화(1CU주)</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>변화</t>
-        </is>
-      </c>
       <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
@@ -626,20 +648,26 @@
       <c r="B6" s="11" t="n">
         <v>111</v>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="n">
+        <v>1107569100</v>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>409→520</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>아모그린텍  (편출)</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="G6" s="14" t="n">
         <v>-97</v>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="H6" s="14" t="n">
+        <v>-698074080</v>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>97→0</t>
         </is>
@@ -654,20 +682,26 @@
       <c r="B7" s="11" t="n">
         <v>59</v>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="11" t="n">
+        <v>2800175400</v>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>0→59</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>파두</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="G7" s="14" t="n">
         <v>-97</v>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="H7" s="14" t="n">
+        <v>-8776075000</v>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>116→19</t>
         </is>
@@ -682,20 +716,26 @@
       <c r="B8" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="11" t="n">
+        <v>3330410600</v>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>102→133</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>두산테스나</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="G8" s="14" t="n">
         <v>-47</v>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="H8" s="14" t="n">
+        <v>-5651947400</v>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>108→61</t>
         </is>
@@ -710,20 +750,26 @@
       <c r="B9" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="11" t="n">
+        <v>1187032000</v>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>28→56</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>성일하이텍  (편출)</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="G9" s="14" t="n">
         <v>-39</v>
       </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="H9" s="14" t="n">
+        <v>-1736034300</v>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
         <is>
           <t>39→0</t>
         </is>
@@ -738,20 +784,26 @@
       <c r="B10" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="11" t="n">
+        <v>522170000</v>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>157→182</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>비나텍</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="G10" s="14" t="n">
         <v>-19</v>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="H10" s="14" t="n">
+        <v>-1628653400</v>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>76→57</t>
         </is>
@@ -760,26 +812,32 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>28→43</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="C11" s="11" t="n">
+        <v>2607231000</v>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>25→40</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>삼현  (편출)</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="G11" s="14" t="n">
         <v>-9</v>
       </c>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="H11" s="14" t="n">
+        <v>-355023900</v>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t>9→0</t>
         </is>
@@ -788,20 +846,24 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>25→40</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="n"/>
+      <c r="C12" s="11" t="n">
+        <v>2050422000</v>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>28→43</t>
+        </is>
+      </c>
       <c r="F12" s="15" t="n"/>
       <c r="G12" s="15" t="n"/>
+      <c r="H12" s="15" t="n"/>
+      <c r="I12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -812,14 +874,18 @@
       <c r="B13" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="11" t="n">
+        <v>2384817600</v>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>30→42</t>
         </is>
       </c>
-      <c r="E13" s="15" t="n"/>
       <c r="F13" s="15" t="n"/>
       <c r="G13" s="15" t="n"/>
+      <c r="H13" s="15" t="n"/>
+      <c r="I13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -830,14 +896,18 @@
       <c r="B14" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="11" t="n">
+        <v>3753420000</v>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>27→37</t>
         </is>
       </c>
-      <c r="E14" s="15" t="n"/>
       <c r="F14" s="15" t="n"/>
       <c r="G14" s="15" t="n"/>
+      <c r="H14" s="15" t="n"/>
+      <c r="I14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -848,14 +918,18 @@
       <c r="B15" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="11" t="n">
+        <v>1881880000</v>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>38→45</t>
         </is>
       </c>
-      <c r="E15" s="15" t="n"/>
       <c r="F15" s="15" t="n"/>
       <c r="G15" s="15" t="n"/>
+      <c r="H15" s="15" t="n"/>
+      <c r="I15" s="15" t="n"/>
     </row>
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -869,6 +943,8 @@
       <c r="E17" s="4" t="n"/>
       <c r="F17" s="4" t="n"/>
       <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -878,13 +954,15 @@
       </c>
       <c r="B18" s="6" t="n"/>
       <c r="C18" s="6" t="n"/>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="D18" s="6" t="n"/>
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
@@ -894,25 +972,35 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>변화</t>
+          <t>변화(1CU주)</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>변화</t>
-        </is>
-      </c>
       <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
@@ -927,20 +1015,26 @@
       <c r="B20" s="11" t="n">
         <v>493</v>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="11" t="n">
+        <v>11440558000</v>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>493→986</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>한스바이오메드  (편출)</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n">
+      <c r="G20" s="14" t="n">
         <v>-87</v>
       </c>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="H20" s="14" t="n">
+        <v>-1083324000</v>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
         <is>
           <t>87→0</t>
         </is>
@@ -955,20 +1049,26 @@
       <c r="B21" s="11" t="n">
         <v>67</v>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="11" t="n">
+        <v>459993860</v>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>916→983</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>인벤티지랩  (편출)</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n">
+      <c r="G21" s="14" t="n">
         <v>-58</v>
       </c>
-      <c r="G21" s="12" t="inlineStr">
+      <c r="H21" s="14" t="n">
+        <v>-1260595200</v>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
         <is>
           <t>58→0</t>
         </is>
@@ -983,20 +1083,26 @@
       <c r="B22" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="11" t="n">
+        <v>1407925000</v>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>657→682</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>보로노이</t>
         </is>
       </c>
-      <c r="F22" s="14" t="n">
+      <c r="G22" s="14" t="n">
         <v>-20</v>
       </c>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="H22" s="14" t="n">
+        <v>-2113444000</v>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
         <is>
           <t>127→107</t>
         </is>
@@ -1011,14 +1117,18 @@
       <c r="B23" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="11" t="n">
+        <v>2249850000</v>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>90→100</t>
         </is>
       </c>
-      <c r="E23" s="15" t="n"/>
       <c r="F23" s="15" t="n"/>
       <c r="G23" s="15" t="n"/>
+      <c r="H23" s="15" t="n"/>
+      <c r="I23" s="15" t="n"/>
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -1032,6 +1142,8 @@
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="n"/>
       <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -1041,13 +1153,15 @@
       </c>
       <c r="B26" s="6" t="n"/>
       <c r="C26" s="6" t="n"/>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="D26" s="6" t="n"/>
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
@@ -1057,25 +1171,35 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>변화</t>
+          <t>변화(1CU주)</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>변화</t>
-        </is>
-      </c>
       <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
@@ -1090,20 +1214,26 @@
       <c r="B28" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C28" s="11" t="n">
+        <v>1239840000</v>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>40→80</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="F28" s="13" t="inlineStr">
         <is>
           <t>HPSP</t>
         </is>
       </c>
-      <c r="F28" s="14" t="n">
+      <c r="G28" s="14" t="n">
         <v>-149</v>
       </c>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="H28" s="14" t="n">
+        <v>-6082776000</v>
+      </c>
+      <c r="I28" s="12" t="inlineStr">
         <is>
           <t>351→202</t>
         </is>
@@ -1118,20 +1248,26 @@
       <c r="B29" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C29" s="11" t="n">
+        <v>7095816000</v>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>23→49</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="F29" s="13" t="inlineStr">
         <is>
           <t>서진시스템</t>
         </is>
       </c>
-      <c r="F29" s="14" t="n">
+      <c r="G29" s="14" t="n">
         <v>-87</v>
       </c>
-      <c r="G29" s="12" t="inlineStr">
+      <c r="H29" s="14" t="n">
+        <v>-3453030000</v>
+      </c>
+      <c r="I29" s="12" t="inlineStr">
         <is>
           <t>149→62</t>
         </is>
@@ -1146,20 +1282,26 @@
       <c r="B30" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C30" s="11" t="n">
+        <v>1001700000</v>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>0→25</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="F30" s="13" t="inlineStr">
         <is>
           <t>제주반도체</t>
         </is>
       </c>
-      <c r="F30" s="14" t="n">
+      <c r="G30" s="14" t="n">
         <v>-60</v>
       </c>
-      <c r="G30" s="12" t="inlineStr">
+      <c r="H30" s="14" t="n">
+        <v>-4712904000</v>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
         <is>
           <t>210→150</t>
         </is>
@@ -1174,20 +1316,26 @@
       <c r="B31" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C31" s="11" t="n">
+        <v>1306594800</v>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>99→120</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="F31" s="13" t="inlineStr">
         <is>
           <t>한선엔지니어링</t>
         </is>
       </c>
-      <c r="F31" s="14" t="n">
+      <c r="G31" s="14" t="n">
         <v>-7</v>
       </c>
-      <c r="G31" s="12" t="inlineStr">
+      <c r="H31" s="14" t="n">
+        <v>-76098960</v>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
         <is>
           <t>220→213</t>
         </is>
@@ -1202,14 +1350,18 @@
       <c r="B32" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C32" s="11" t="n">
+        <v>2470305600</v>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>19→40</t>
         </is>
       </c>
-      <c r="E32" s="15" t="n"/>
       <c r="F32" s="15" t="n"/>
       <c r="G32" s="15" t="n"/>
+      <c r="H32" s="15" t="n"/>
+      <c r="I32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
@@ -1220,14 +1372,18 @@
       <c r="B33" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C33" s="11" t="n">
+        <v>2816780400</v>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>60→79</t>
         </is>
       </c>
-      <c r="E33" s="15" t="n"/>
       <c r="F33" s="15" t="n"/>
       <c r="G33" s="15" t="n"/>
+      <c r="H33" s="15" t="n"/>
+      <c r="I33" s="15" t="n"/>
     </row>
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
@@ -1241,6 +1397,8 @@
       <c r="E35" s="4" t="n"/>
       <c r="F35" s="4" t="n"/>
       <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n"/>
+      <c r="I35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -1250,13 +1408,15 @@
       </c>
       <c r="B36" s="6" t="n"/>
       <c r="C36" s="6" t="n"/>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="D36" s="6" t="n"/>
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
@@ -1266,25 +1426,35 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>변화</t>
+          <t>변화(1CU주)</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="F37" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>변화</t>
-        </is>
-      </c>
       <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
@@ -1299,20 +1469,26 @@
       <c r="B38" s="11" t="n">
         <v>170</v>
       </c>
-      <c r="C38" s="12" t="inlineStr">
+      <c r="C38" s="11" t="n">
+        <v>2725270000</v>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>170→340</t>
         </is>
       </c>
-      <c r="E38" s="13" t="inlineStr">
+      <c r="F38" s="13" t="inlineStr">
         <is>
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="F38" s="14" t="n">
+      <c r="G38" s="14" t="n">
         <v>-5</v>
       </c>
-      <c r="G38" s="12" t="inlineStr">
+      <c r="H38" s="14" t="n">
+        <v>-338801500</v>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
         <is>
           <t>500→495</t>
         </is>
@@ -1330,6 +1506,8 @@
       <c r="E40" s="4" t="n"/>
       <c r="F40" s="4" t="n"/>
       <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -1339,13 +1517,15 @@
       </c>
       <c r="B41" s="6" t="n"/>
       <c r="C41" s="6" t="n"/>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="D41" s="6" t="n"/>
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
+      <c r="H41" s="8" t="n"/>
+      <c r="I41" s="8" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
@@ -1355,25 +1535,35 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>변화</t>
+          <t>변화(1CU주)</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr">
+      <c r="F42" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>변화</t>
-        </is>
-      </c>
       <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
@@ -1388,20 +1578,30 @@
       <c r="B43" s="11" t="n">
         <v>175</v>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C43" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
         <is>
           <t>2,845→3,020</t>
         </is>
       </c>
-      <c r="E43" s="13" t="inlineStr">
+      <c r="F43" s="13" t="inlineStr">
         <is>
           <t>씨어스</t>
         </is>
       </c>
-      <c r="F43" s="14" t="n">
+      <c r="G43" s="14" t="n">
         <v>-188</v>
       </c>
-      <c r="G43" s="12" t="inlineStr">
+      <c r="H43" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I43" s="12" t="inlineStr">
         <is>
           <t>944→756</t>
         </is>
@@ -1416,20 +1616,30 @@
       <c r="B44" s="11" t="n">
         <v>111</v>
       </c>
-      <c r="C44" s="12" t="inlineStr">
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
         <is>
           <t>399→510</t>
         </is>
       </c>
-      <c r="E44" s="13" t="inlineStr">
+      <c r="F44" s="13" t="inlineStr">
         <is>
           <t>디아이티  (편출)</t>
         </is>
       </c>
-      <c r="F44" s="14" t="n">
+      <c r="G44" s="14" t="n">
         <v>-50</v>
       </c>
-      <c r="G44" s="12" t="inlineStr">
+      <c r="H44" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr">
         <is>
           <t>50→0</t>
         </is>
@@ -1444,20 +1654,30 @@
       <c r="B45" s="11" t="n">
         <v>110</v>
       </c>
-      <c r="C45" s="12" t="inlineStr">
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
         <is>
           <t>430→540</t>
         </is>
       </c>
-      <c r="E45" s="13" t="inlineStr">
+      <c r="F45" s="13" t="inlineStr">
         <is>
           <t>레이크머티리얼즈</t>
         </is>
       </c>
-      <c r="F45" s="14" t="n">
+      <c r="G45" s="14" t="n">
         <v>-43</v>
       </c>
-      <c r="G45" s="12" t="inlineStr">
+      <c r="H45" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I45" s="12" t="inlineStr">
         <is>
           <t>73→30</t>
         </is>
@@ -1472,20 +1692,30 @@
       <c r="B46" s="11" t="n">
         <v>108</v>
       </c>
-      <c r="C46" s="12" t="inlineStr">
+      <c r="C46" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
         <is>
           <t>547→655</t>
         </is>
       </c>
-      <c r="E46" s="13" t="inlineStr">
+      <c r="F46" s="13" t="inlineStr">
         <is>
           <t>에이프릴바이오  (편출)</t>
         </is>
       </c>
-      <c r="F46" s="14" t="n">
+      <c r="G46" s="14" t="n">
         <v>-40</v>
       </c>
-      <c r="G46" s="12" t="inlineStr">
+      <c r="H46" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I46" s="12" t="inlineStr">
         <is>
           <t>40→0</t>
         </is>
@@ -1500,20 +1730,30 @@
       <c r="B47" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="C47" s="12" t="inlineStr">
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
         <is>
           <t>181→210</t>
         </is>
       </c>
-      <c r="E47" s="13" t="inlineStr">
+      <c r="F47" s="13" t="inlineStr">
         <is>
           <t>새로닉스</t>
         </is>
       </c>
-      <c r="F47" s="14" t="n">
+      <c r="G47" s="14" t="n">
         <v>-28</v>
       </c>
-      <c r="G47" s="12" t="inlineStr">
+      <c r="H47" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I47" s="12" t="inlineStr">
         <is>
           <t>978→950</t>
         </is>
@@ -1528,20 +1768,30 @@
       <c r="B48" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="C48" s="12" t="inlineStr">
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
         <is>
           <t>58→85</t>
         </is>
       </c>
-      <c r="E48" s="13" t="inlineStr">
+      <c r="F48" s="13" t="inlineStr">
         <is>
           <t>덕산네오룩스</t>
         </is>
       </c>
-      <c r="F48" s="14" t="n">
+      <c r="G48" s="14" t="n">
         <v>-28</v>
       </c>
-      <c r="G48" s="12" t="inlineStr">
+      <c r="H48" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="inlineStr">
         <is>
           <t>42→14</t>
         </is>
@@ -1556,20 +1806,30 @@
       <c r="B49" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="C49" s="12" t="inlineStr">
+      <c r="C49" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
         <is>
           <t>587→612</t>
         </is>
       </c>
-      <c r="E49" s="13" t="inlineStr">
+      <c r="F49" s="13" t="inlineStr">
         <is>
           <t>씨젠</t>
         </is>
       </c>
-      <c r="F49" s="14" t="n">
+      <c r="G49" s="14" t="n">
         <v>-17</v>
       </c>
-      <c r="G49" s="12" t="inlineStr">
+      <c r="H49" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" s="12" t="inlineStr">
         <is>
           <t>33→16</t>
         </is>
@@ -1584,20 +1844,30 @@
       <c r="B50" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="C50" s="12" t="inlineStr">
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
         <is>
           <t>81→102</t>
         </is>
       </c>
-      <c r="E50" s="13" t="inlineStr">
+      <c r="F50" s="13" t="inlineStr">
         <is>
           <t>클래시스</t>
         </is>
       </c>
-      <c r="F50" s="14" t="n">
+      <c r="G50" s="14" t="n">
         <v>-17</v>
       </c>
-      <c r="G50" s="12" t="inlineStr">
+      <c r="H50" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="inlineStr">
         <is>
           <t>73→56</t>
         </is>
@@ -1612,20 +1882,30 @@
       <c r="B51" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="C51" s="12" t="inlineStr">
+      <c r="C51" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
         <is>
           <t>60→77</t>
         </is>
       </c>
-      <c r="E51" s="13" t="inlineStr">
+      <c r="F51" s="13" t="inlineStr">
         <is>
           <t>실리콘투</t>
         </is>
       </c>
-      <c r="F51" s="14" t="n">
+      <c r="G51" s="14" t="n">
         <v>-15</v>
       </c>
-      <c r="G51" s="12" t="inlineStr">
+      <c r="H51" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="12" t="inlineStr">
         <is>
           <t>100→85</t>
         </is>
@@ -1640,22 +1920,32 @@
       <c r="B52" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="C52" s="12" t="inlineStr">
+      <c r="C52" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
         <is>
           <t>125→140</t>
         </is>
       </c>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>기가비스</t>
-        </is>
-      </c>
-      <c r="F52" s="14" t="n">
+      <c r="F52" s="13" t="inlineStr">
+        <is>
+          <t>알지노믹스  (편출)</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="n">
         <v>-11</v>
       </c>
-      <c r="G52" s="12" t="inlineStr">
-        <is>
-          <t>47→36</t>
+      <c r="H52" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" s="12" t="inlineStr">
+        <is>
+          <t>11→0</t>
         </is>
       </c>
     </row>
@@ -1668,22 +1958,32 @@
       <c r="B53" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C53" s="12" t="inlineStr">
+      <c r="C53" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
         <is>
           <t>0→11</t>
         </is>
       </c>
-      <c r="E53" s="13" t="inlineStr">
-        <is>
-          <t>알지노믹스  (편출)</t>
-        </is>
-      </c>
-      <c r="F53" s="14" t="n">
+      <c r="F53" s="13" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="n">
         <v>-11</v>
       </c>
-      <c r="G53" s="12" t="inlineStr">
-        <is>
-          <t>11→0</t>
+      <c r="H53" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I53" s="12" t="inlineStr">
+        <is>
+          <t>47→36</t>
         </is>
       </c>
     </row>
@@ -1696,22 +1996,32 @@
       <c r="B54" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C54" s="12" t="inlineStr">
+      <c r="C54" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
         <is>
           <t>29→40</t>
         </is>
       </c>
-      <c r="E54" s="13" t="inlineStr">
-        <is>
-          <t>피에스케이홀딩스</t>
-        </is>
-      </c>
-      <c r="F54" s="14" t="n">
+      <c r="F54" s="13" t="inlineStr">
+        <is>
+          <t>파크시스템스</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="n">
         <v>-9</v>
       </c>
-      <c r="G54" s="12" t="inlineStr">
-        <is>
-          <t>116→107</t>
+      <c r="H54" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" s="12" t="inlineStr">
+        <is>
+          <t>41→32</t>
         </is>
       </c>
     </row>
@@ -1724,22 +2034,32 @@
       <c r="B55" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C55" s="12" t="inlineStr">
+      <c r="C55" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
         <is>
           <t>60→68</t>
         </is>
       </c>
-      <c r="E55" s="13" t="inlineStr">
-        <is>
-          <t>파크시스템스</t>
-        </is>
-      </c>
-      <c r="F55" s="14" t="n">
+      <c r="F55" s="13" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="n">
         <v>-9</v>
       </c>
-      <c r="G55" s="12" t="inlineStr">
-        <is>
-          <t>41→32</t>
+      <c r="H55" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" s="12" t="inlineStr">
+        <is>
+          <t>116→107</t>
         </is>
       </c>
     </row>
@@ -1752,20 +2072,30 @@
       <c r="B56" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C56" s="12" t="inlineStr">
+      <c r="C56" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
         <is>
           <t>52→60</t>
         </is>
       </c>
-      <c r="E56" s="13" t="inlineStr">
+      <c r="F56" s="13" t="inlineStr">
         <is>
           <t>리가켐바이오</t>
         </is>
       </c>
-      <c r="F56" s="14" t="n">
+      <c r="G56" s="14" t="n">
         <v>-6</v>
       </c>
-      <c r="G56" s="12" t="inlineStr">
+      <c r="H56" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" s="12" t="inlineStr">
         <is>
           <t>13→7</t>
         </is>
@@ -1780,20 +2110,30 @@
       <c r="B57" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="C57" s="12" t="inlineStr">
+      <c r="C57" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
         <is>
           <t>39→46</t>
         </is>
       </c>
-      <c r="E57" s="13" t="inlineStr">
+      <c r="F57" s="13" t="inlineStr">
         <is>
           <t>코오롱티슈진</t>
         </is>
       </c>
-      <c r="F57" s="14" t="n">
+      <c r="G57" s="14" t="n">
         <v>-3</v>
       </c>
-      <c r="G57" s="12" t="inlineStr">
+      <c r="H57" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I57" s="12" t="inlineStr">
         <is>
           <t>80→77</t>
         </is>
@@ -1808,14 +2148,20 @@
       <c r="B58" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C58" s="12" t="inlineStr">
+      <c r="C58" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
         <is>
           <t>0→4</t>
         </is>
       </c>
-      <c r="E58" s="15" t="n"/>
       <c r="F58" s="15" t="n"/>
       <c r="G58" s="15" t="n"/>
+      <c r="H58" s="15" t="n"/>
+      <c r="I58" s="15" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
@@ -1826,14 +2172,20 @@
       <c r="B59" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C59" s="12" t="inlineStr">
+      <c r="C59" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
         <is>
           <t>41→44</t>
         </is>
       </c>
-      <c r="E59" s="15" t="n"/>
       <c r="F59" s="15" t="n"/>
       <c r="G59" s="15" t="n"/>
+      <c r="H59" s="15" t="n"/>
+      <c r="I59" s="15" t="n"/>
     </row>
     <row r="61" ht="19" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
@@ -1847,6 +2199,8 @@
       <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="n"/>
       <c r="G61" s="4" t="n"/>
+      <c r="H61" s="4" t="n"/>
+      <c r="I61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -1856,13 +2210,15 @@
       </c>
       <c r="B62" s="6" t="n"/>
       <c r="C62" s="6" t="n"/>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="D62" s="6" t="n"/>
+      <c r="F62" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
+      <c r="H62" s="8" t="n"/>
+      <c r="I62" s="8" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
@@ -1872,25 +2228,35 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>변화</t>
+          <t>변화(1CU주)</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="E63" s="9" t="inlineStr">
+      <c r="F63" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="F63" s="9" t="inlineStr">
-        <is>
-          <t>변화</t>
-        </is>
-      </c>
       <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
@@ -1905,20 +2271,26 @@
       <c r="B64" s="11" t="n">
         <v>184</v>
       </c>
-      <c r="C64" s="12" t="inlineStr">
+      <c r="C64" s="11" t="n">
+        <v>844928000</v>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
         <is>
           <t>184→368</t>
         </is>
       </c>
-      <c r="E64" s="13" t="inlineStr">
+      <c r="F64" s="13" t="inlineStr">
         <is>
           <t>HLB이노베이션  (편출)</t>
         </is>
       </c>
-      <c r="F64" s="14" t="n">
+      <c r="G64" s="14" t="n">
         <v>-622</v>
       </c>
-      <c r="G64" s="12" t="inlineStr">
+      <c r="H64" s="14" t="n">
+        <v>-849900800</v>
+      </c>
+      <c r="I64" s="12" t="inlineStr">
         <is>
           <t>622→0</t>
         </is>
@@ -1933,20 +2305,26 @@
       <c r="B65" s="11" t="n">
         <v>44</v>
       </c>
-      <c r="C65" s="12" t="inlineStr">
+      <c r="C65" s="11" t="n">
+        <v>431200000</v>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
         <is>
           <t>354→398</t>
         </is>
       </c>
-      <c r="E65" s="13" t="inlineStr">
+      <c r="F65" s="13" t="inlineStr">
         <is>
           <t>에스바이오메딕스  (편출)</t>
         </is>
       </c>
-      <c r="F65" s="14" t="n">
+      <c r="G65" s="14" t="n">
         <v>-214</v>
       </c>
-      <c r="G65" s="12" t="inlineStr">
+      <c r="H65" s="14" t="n">
+        <v>-486550400</v>
+      </c>
+      <c r="I65" s="12" t="inlineStr">
         <is>
           <t>214→0</t>
         </is>
@@ -1961,20 +2339,26 @@
       <c r="B66" s="11" t="n">
         <v>32</v>
       </c>
-      <c r="C66" s="12" t="inlineStr">
+      <c r="C66" s="11" t="n">
+        <v>1300992000</v>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
         <is>
           <t>0→32</t>
         </is>
       </c>
-      <c r="E66" s="13" t="inlineStr">
+      <c r="F66" s="13" t="inlineStr">
         <is>
           <t>지투지바이오  (편출)</t>
         </is>
       </c>
-      <c r="F66" s="14" t="n">
+      <c r="G66" s="14" t="n">
         <v>-136</v>
       </c>
-      <c r="G66" s="12" t="inlineStr">
+      <c r="H66" s="14" t="n">
+        <v>-573484800</v>
+      </c>
+      <c r="I66" s="12" t="inlineStr">
         <is>
           <t>136→0</t>
         </is>
@@ -1989,20 +2373,26 @@
       <c r="B67" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="C67" s="12" t="inlineStr">
+      <c r="C67" s="11" t="n">
+        <v>578760000</v>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
         <is>
           <t>46→59</t>
         </is>
       </c>
-      <c r="E67" s="13" t="inlineStr">
+      <c r="F67" s="13" t="inlineStr">
         <is>
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="F67" s="14" t="n">
+      <c r="G67" s="14" t="n">
         <v>-17</v>
       </c>
-      <c r="G67" s="12" t="inlineStr">
+      <c r="H67" s="14" t="n">
+        <v>-687344000</v>
+      </c>
+      <c r="I67" s="12" t="inlineStr">
         <is>
           <t>174→157</t>
         </is>
@@ -2017,51 +2407,57 @@
       <c r="B68" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="C68" s="12" t="inlineStr">
+      <c r="C68" s="11" t="n">
+        <v>185774400</v>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
         <is>
           <t>53→62</t>
         </is>
       </c>
-      <c r="E68" s="15" t="n"/>
       <c r="F68" s="15" t="n"/>
       <c r="G68" s="15" t="n"/>
+      <c r="H68" s="15" t="n"/>
+      <c r="I68" s="15" t="n"/>
     </row>
     <row r="70" ht="19" customHeight="1">
-      <c r="A70" s="16" t="inlineStr">
+      <c r="A70" s="18" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B70" s="17" t="n"/>
-      <c r="C70" s="17" t="n"/>
-      <c r="D70" s="17" t="n"/>
-      <c r="E70" s="17" t="n"/>
-      <c r="F70" s="17" t="n"/>
-      <c r="G70" s="17" t="n"/>
+      <c r="B70" s="19" t="n"/>
+      <c r="C70" s="19" t="n"/>
+      <c r="D70" s="19" t="n"/>
+      <c r="E70" s="19" t="n"/>
+      <c r="F70" s="19" t="n"/>
+      <c r="G70" s="19" t="n"/>
+      <c r="H70" s="19" t="n"/>
+      <c r="I70" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A61:G61"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="A70:G70"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="F62:I62"/>
+    <mergeCell ref="A70:I70"/>
+    <mergeCell ref="A61:I61"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260701.xlsx
+++ b/reports/pdf_rolling5_20260701.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
+    <numFmt numFmtId="165" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;;0"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -128,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -153,11 +154,17 @@
     <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -536,18 +543,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="3" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -567,7 +576,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      오늘 2026-07-01  vs  5일전 2026-06-24      매수 10종목  /  매도 6종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,782억      오늘 2026-07-01  vs  5일전 2026-06-24      매수 10종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -578,6 +587,8 @@
       <c r="G3" s="4" t="n"/>
       <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -588,14 +599,16 @@
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="E4" s="6" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="G4" s="8" t="n"/>
       <c r="H4" s="8" t="n"/>
       <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -615,25 +628,35 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
+          <t>전체대비비중</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>전체대비비중</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
@@ -651,23 +674,29 @@
       <c r="C6" s="11" t="n">
         <v>1107569100</v>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="12" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>409→520</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>아모그린텍  (편출)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="H6" s="15" t="n">
         <v>-97</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="I6" s="15" t="n">
         <v>-698074080</v>
       </c>
-      <c r="I6" s="12" t="inlineStr">
+      <c r="J6" s="16" t="n">
+        <v>-0.121</v>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
         <is>
           <t>97→0</t>
         </is>
@@ -685,23 +714,29 @@
       <c r="C7" s="11" t="n">
         <v>2800175400</v>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="12" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>0→59</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>파두</t>
         </is>
       </c>
-      <c r="G7" s="14" t="n">
+      <c r="H7" s="15" t="n">
         <v>-97</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="I7" s="15" t="n">
         <v>-8776075000</v>
       </c>
-      <c r="I7" s="12" t="inlineStr">
+      <c r="J7" s="16" t="n">
+        <v>-1.518</v>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
         <is>
           <t>116→19</t>
         </is>
@@ -719,23 +754,29 @@
       <c r="C8" s="11" t="n">
         <v>3330410600</v>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="12" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>102→133</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>두산테스나</t>
         </is>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="H8" s="15" t="n">
         <v>-47</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="I8" s="15" t="n">
         <v>-5651947400</v>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="J8" s="16" t="n">
+        <v>-0.977</v>
+      </c>
+      <c r="K8" s="13" t="inlineStr">
         <is>
           <t>108→61</t>
         </is>
@@ -753,23 +794,29 @@
       <c r="C9" s="11" t="n">
         <v>1187032000</v>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="12" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>28→56</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>성일하이텍  (편출)</t>
         </is>
       </c>
-      <c r="G9" s="14" t="n">
+      <c r="H9" s="15" t="n">
         <v>-39</v>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="I9" s="15" t="n">
         <v>-1736034300</v>
       </c>
-      <c r="I9" s="12" t="inlineStr">
+      <c r="J9" s="16" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>39→0</t>
         </is>
@@ -787,23 +834,29 @@
       <c r="C10" s="11" t="n">
         <v>522170000</v>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>157→182</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>비나텍</t>
         </is>
       </c>
-      <c r="G10" s="14" t="n">
+      <c r="H10" s="15" t="n">
         <v>-19</v>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="I10" s="15" t="n">
         <v>-1628653400</v>
       </c>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="J10" s="16" t="n">
+        <v>-0.282</v>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
         <is>
           <t>76→57</t>
         </is>
@@ -812,32 +865,38 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2607231000</v>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>25→40</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
+        <v>2050422000</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>28→43</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>삼현  (편출)</t>
         </is>
       </c>
-      <c r="G11" s="14" t="n">
+      <c r="H11" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="H11" s="14" t="n">
+      <c r="I11" s="15" t="n">
         <v>-355023900</v>
       </c>
-      <c r="I11" s="12" t="inlineStr">
+      <c r="J11" s="16" t="n">
+        <v>-0.061</v>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
         <is>
           <t>9→0</t>
         </is>
@@ -846,24 +905,28 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2050422000</v>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>28→43</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="n"/>
-      <c r="G12" s="15" t="n"/>
-      <c r="H12" s="15" t="n"/>
-      <c r="I12" s="15" t="n"/>
+        <v>2607231000</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>25→40</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="n"/>
+      <c r="H12" s="17" t="n"/>
+      <c r="I12" s="17" t="n"/>
+      <c r="J12" s="17" t="n"/>
+      <c r="K12" s="17" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -877,15 +940,19 @@
       <c r="C13" s="11" t="n">
         <v>2384817600</v>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="12" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>30→42</t>
         </is>
       </c>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
-      <c r="H13" s="15" t="n"/>
-      <c r="I13" s="15" t="n"/>
+      <c r="G13" s="17" t="n"/>
+      <c r="H13" s="17" t="n"/>
+      <c r="I13" s="17" t="n"/>
+      <c r="J13" s="17" t="n"/>
+      <c r="K13" s="17" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -899,15 +966,19 @@
       <c r="C14" s="11" t="n">
         <v>3753420000</v>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="12" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>27→37</t>
         </is>
       </c>
-      <c r="F14" s="15" t="n"/>
-      <c r="G14" s="15" t="n"/>
-      <c r="H14" s="15" t="n"/>
-      <c r="I14" s="15" t="n"/>
+      <c r="G14" s="17" t="n"/>
+      <c r="H14" s="17" t="n"/>
+      <c r="I14" s="17" t="n"/>
+      <c r="J14" s="17" t="n"/>
+      <c r="K14" s="17" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -921,20 +992,24 @@
       <c r="C15" s="11" t="n">
         <v>1881880000</v>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="12" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>38→45</t>
         </is>
       </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
-      <c r="H15" s="15" t="n"/>
-      <c r="I15" s="15" t="n"/>
+      <c r="G15" s="17" t="n"/>
+      <c r="H15" s="17" t="n"/>
+      <c r="I15" s="17" t="n"/>
+      <c r="J15" s="17" t="n"/>
+      <c r="K15" s="17" t="n"/>
     </row>
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      오늘 2026-07-01  vs  5일전 2026-06-24      매수 4종목  /  매도 3종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,784억      오늘 2026-07-01  vs  5일전 2026-06-24      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -945,6 +1020,8 @@
       <c r="G17" s="4" t="n"/>
       <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -955,14 +1032,16 @@
       <c r="B18" s="6" t="n"/>
       <c r="C18" s="6" t="n"/>
       <c r="D18" s="6" t="n"/>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="E18" s="6" t="n"/>
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="G18" s="8" t="n"/>
       <c r="H18" s="8" t="n"/>
       <c r="I18" s="8" t="n"/>
+      <c r="J18" s="8" t="n"/>
+      <c r="K18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
@@ -982,25 +1061,35 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
+          <t>전체대비비중</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="H19" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>전체대비비중</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
@@ -1018,23 +1107,29 @@
       <c r="C20" s="11" t="n">
         <v>11440558000</v>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="12" t="n">
+        <v>2.391</v>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>493→986</t>
         </is>
       </c>
-      <c r="F20" s="13" t="inlineStr">
+      <c r="G20" s="14" t="inlineStr">
         <is>
           <t>한스바이오메드  (편출)</t>
         </is>
       </c>
-      <c r="G20" s="14" t="n">
+      <c r="H20" s="15" t="n">
         <v>-87</v>
       </c>
-      <c r="H20" s="14" t="n">
+      <c r="I20" s="15" t="n">
         <v>-1083324000</v>
       </c>
-      <c r="I20" s="12" t="inlineStr">
+      <c r="J20" s="16" t="n">
+        <v>-0.226</v>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
         <is>
           <t>87→0</t>
         </is>
@@ -1052,23 +1147,29 @@
       <c r="C21" s="11" t="n">
         <v>459993860</v>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="12" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>916→983</t>
         </is>
       </c>
-      <c r="F21" s="13" t="inlineStr">
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>인벤티지랩  (편출)</t>
         </is>
       </c>
-      <c r="G21" s="14" t="n">
+      <c r="H21" s="15" t="n">
         <v>-58</v>
       </c>
-      <c r="H21" s="14" t="n">
+      <c r="I21" s="15" t="n">
         <v>-1260595200</v>
       </c>
-      <c r="I21" s="12" t="inlineStr">
+      <c r="J21" s="16" t="n">
+        <v>-0.263</v>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
         <is>
           <t>58→0</t>
         </is>
@@ -1086,23 +1187,29 @@
       <c r="C22" s="11" t="n">
         <v>1407925000</v>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="12" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>657→682</t>
         </is>
       </c>
-      <c r="F22" s="13" t="inlineStr">
+      <c r="G22" s="14" t="inlineStr">
         <is>
           <t>보로노이</t>
         </is>
       </c>
-      <c r="G22" s="14" t="n">
+      <c r="H22" s="15" t="n">
         <v>-20</v>
       </c>
-      <c r="H22" s="14" t="n">
+      <c r="I22" s="15" t="n">
         <v>-2113444000</v>
       </c>
-      <c r="I22" s="12" t="inlineStr">
+      <c r="J22" s="16" t="n">
+        <v>-0.442</v>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
         <is>
           <t>127→107</t>
         </is>
@@ -1120,20 +1227,24 @@
       <c r="C23" s="11" t="n">
         <v>2249850000</v>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="12" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>90→100</t>
         </is>
       </c>
-      <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
-      <c r="H23" s="15" t="n"/>
-      <c r="I23" s="15" t="n"/>
+      <c r="G23" s="17" t="n"/>
+      <c r="H23" s="17" t="n"/>
+      <c r="I23" s="17" t="n"/>
+      <c r="J23" s="17" t="n"/>
+      <c r="K23" s="17" t="n"/>
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      오늘 2026-07-01  vs  5일전 2026-06-24      매수 6종목  /  매도 4종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,651억      오늘 2026-07-01  vs  5일전 2026-06-24      매수 6종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1144,6 +1255,8 @@
       <c r="G25" s="4" t="n"/>
       <c r="H25" s="4" t="n"/>
       <c r="I25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
+      <c r="K25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -1154,14 +1267,16 @@
       <c r="B26" s="6" t="n"/>
       <c r="C26" s="6" t="n"/>
       <c r="D26" s="6" t="n"/>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="E26" s="6" t="n"/>
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
       <c r="I26" s="8" t="n"/>
+      <c r="J26" s="8" t="n"/>
+      <c r="K26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
@@ -1181,25 +1296,35 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
+          <t>전체대비비중</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
+        <is>
+          <t>전체대비비중</t>
+        </is>
+      </c>
+      <c r="K27" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
@@ -1217,23 +1342,29 @@
       <c r="C28" s="11" t="n">
         <v>1239840000</v>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>40→80</t>
         </is>
       </c>
-      <c r="F28" s="13" t="inlineStr">
+      <c r="G28" s="14" t="inlineStr">
         <is>
           <t>HPSP</t>
         </is>
       </c>
-      <c r="G28" s="14" t="n">
+      <c r="H28" s="15" t="n">
         <v>-149</v>
       </c>
-      <c r="H28" s="14" t="n">
+      <c r="I28" s="15" t="n">
         <v>-6082776000</v>
       </c>
-      <c r="I28" s="12" t="inlineStr">
+      <c r="J28" s="16" t="n">
+        <v>-1.666</v>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
         <is>
           <t>351→202</t>
         </is>
@@ -1251,23 +1382,29 @@
       <c r="C29" s="11" t="n">
         <v>7095816000</v>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D29" s="12" t="n">
+        <v>1.943</v>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>23→49</t>
         </is>
       </c>
-      <c r="F29" s="13" t="inlineStr">
+      <c r="G29" s="14" t="inlineStr">
         <is>
           <t>서진시스템</t>
         </is>
       </c>
-      <c r="G29" s="14" t="n">
+      <c r="H29" s="15" t="n">
         <v>-87</v>
       </c>
-      <c r="H29" s="14" t="n">
+      <c r="I29" s="15" t="n">
         <v>-3453030000</v>
       </c>
-      <c r="I29" s="12" t="inlineStr">
+      <c r="J29" s="16" t="n">
+        <v>-0.946</v>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
         <is>
           <t>149→62</t>
         </is>
@@ -1285,23 +1422,29 @@
       <c r="C30" s="11" t="n">
         <v>1001700000</v>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D30" s="12" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>0→25</t>
         </is>
       </c>
-      <c r="F30" s="13" t="inlineStr">
+      <c r="G30" s="14" t="inlineStr">
         <is>
           <t>제주반도체</t>
         </is>
       </c>
-      <c r="G30" s="14" t="n">
+      <c r="H30" s="15" t="n">
         <v>-60</v>
       </c>
-      <c r="H30" s="14" t="n">
+      <c r="I30" s="15" t="n">
         <v>-4712904000</v>
       </c>
-      <c r="I30" s="12" t="inlineStr">
+      <c r="J30" s="16" t="n">
+        <v>-1.291</v>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
         <is>
           <t>210→150</t>
         </is>
@@ -1319,23 +1462,29 @@
       <c r="C31" s="11" t="n">
         <v>1306594800</v>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="12" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>99→120</t>
         </is>
       </c>
-      <c r="F31" s="13" t="inlineStr">
+      <c r="G31" s="14" t="inlineStr">
         <is>
           <t>한선엔지니어링</t>
         </is>
       </c>
-      <c r="G31" s="14" t="n">
+      <c r="H31" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="H31" s="14" t="n">
+      <c r="I31" s="15" t="n">
         <v>-76098960</v>
       </c>
-      <c r="I31" s="12" t="inlineStr">
+      <c r="J31" s="16" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
         <is>
           <t>220→213</t>
         </is>
@@ -1353,15 +1502,19 @@
       <c r="C32" s="11" t="n">
         <v>2470305600</v>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D32" s="12" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>19→40</t>
         </is>
       </c>
-      <c r="F32" s="15" t="n"/>
-      <c r="G32" s="15" t="n"/>
-      <c r="H32" s="15" t="n"/>
-      <c r="I32" s="15" t="n"/>
+      <c r="G32" s="17" t="n"/>
+      <c r="H32" s="17" t="n"/>
+      <c r="I32" s="17" t="n"/>
+      <c r="J32" s="17" t="n"/>
+      <c r="K32" s="17" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
@@ -1375,20 +1528,24 @@
       <c r="C33" s="11" t="n">
         <v>2816780400</v>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="12" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>60→79</t>
         </is>
       </c>
-      <c r="F33" s="15" t="n"/>
-      <c r="G33" s="15" t="n"/>
-      <c r="H33" s="15" t="n"/>
-      <c r="I33" s="15" t="n"/>
+      <c r="G33" s="17" t="n"/>
+      <c r="H33" s="17" t="n"/>
+      <c r="I33" s="17" t="n"/>
+      <c r="J33" s="17" t="n"/>
+      <c r="K33" s="17" t="n"/>
     </row>
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      오늘 2026-07-01  vs  5일전 2026-06-24      매수 1종목  /  매도 1종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,801억      오늘 2026-07-01  vs  5일전 2026-06-24      매수 1종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B35" s="4" t="n"/>
@@ -1399,6 +1556,8 @@
       <c r="G35" s="4" t="n"/>
       <c r="H35" s="4" t="n"/>
       <c r="I35" s="4" t="n"/>
+      <c r="J35" s="4" t="n"/>
+      <c r="K35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -1409,14 +1568,16 @@
       <c r="B36" s="6" t="n"/>
       <c r="C36" s="6" t="n"/>
       <c r="D36" s="6" t="n"/>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="E36" s="6" t="n"/>
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="G36" s="8" t="n"/>
       <c r="H36" s="8" t="n"/>
       <c r="I36" s="8" t="n"/>
+      <c r="J36" s="8" t="n"/>
+      <c r="K36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
@@ -1436,25 +1597,35 @@
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
+          <t>전체대비비중</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="G37" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="H37" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="I37" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>전체대비비중</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
@@ -1472,23 +1643,29 @@
       <c r="C38" s="11" t="n">
         <v>2725270000</v>
       </c>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="D38" s="12" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
         <is>
           <t>170→340</t>
         </is>
       </c>
-      <c r="F38" s="13" t="inlineStr">
+      <c r="G38" s="14" t="inlineStr">
         <is>
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="G38" s="14" t="n">
+      <c r="H38" s="15" t="n">
         <v>-5</v>
       </c>
-      <c r="H38" s="14" t="n">
+      <c r="I38" s="15" t="n">
         <v>-338801500</v>
       </c>
-      <c r="I38" s="12" t="inlineStr">
+      <c r="J38" s="16" t="n">
+        <v>-0.121</v>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
         <is>
           <t>500→495</t>
         </is>
@@ -1497,7 +1674,7 @@
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      오늘 2026-07-01  vs  5일전 2026-06-24      매수 17종목  /  매도 15종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 376억      오늘 2026-07-01  vs  5일전 2026-06-24      매수 17종목  /  매도 15종목</t>
         </is>
       </c>
       <c r="B40" s="4" t="n"/>
@@ -1508,6 +1685,8 @@
       <c r="G40" s="4" t="n"/>
       <c r="H40" s="4" t="n"/>
       <c r="I40" s="4" t="n"/>
+      <c r="J40" s="4" t="n"/>
+      <c r="K40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -1518,14 +1697,16 @@
       <c r="B41" s="6" t="n"/>
       <c r="C41" s="6" t="n"/>
       <c r="D41" s="6" t="n"/>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="E41" s="6" t="n"/>
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="G41" s="8" t="n"/>
       <c r="H41" s="8" t="n"/>
       <c r="I41" s="8" t="n"/>
+      <c r="J41" s="8" t="n"/>
+      <c r="K41" s="8" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
@@ -1545,25 +1726,35 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
+          <t>전체대비비중</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="F42" s="9" t="inlineStr">
+      <c r="G42" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G42" s="9" t="inlineStr">
+      <c r="H42" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="H42" s="9" t="inlineStr">
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="I42" s="9" t="inlineStr">
+      <c r="J42" s="9" t="inlineStr">
+        <is>
+          <t>전체대비비중</t>
+        </is>
+      </c>
+      <c r="K42" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
@@ -1578,30 +1769,40 @@
       <c r="B43" s="11" t="n">
         <v>175</v>
       </c>
-      <c r="C43" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
         <is>
           <t>2,845→3,020</t>
         </is>
       </c>
-      <c r="F43" s="13" t="inlineStr">
+      <c r="G43" s="14" t="inlineStr">
         <is>
           <t>씨어스</t>
         </is>
       </c>
-      <c r="G43" s="14" t="n">
+      <c r="H43" s="15" t="n">
         <v>-188</v>
       </c>
-      <c r="H43" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I43" s="12" t="inlineStr">
+      <c r="I43" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="inlineStr">
         <is>
           <t>944→756</t>
         </is>
@@ -1616,30 +1817,40 @@
       <c r="B44" s="11" t="n">
         <v>111</v>
       </c>
-      <c r="C44" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D44" s="12" t="inlineStr">
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
         <is>
           <t>399→510</t>
         </is>
       </c>
-      <c r="F44" s="13" t="inlineStr">
+      <c r="G44" s="14" t="inlineStr">
         <is>
           <t>디아이티  (편출)</t>
         </is>
       </c>
-      <c r="G44" s="14" t="n">
+      <c r="H44" s="15" t="n">
         <v>-50</v>
       </c>
-      <c r="H44" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I44" s="12" t="inlineStr">
+      <c r="I44" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J44" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="inlineStr">
         <is>
           <t>50→0</t>
         </is>
@@ -1654,30 +1865,40 @@
       <c r="B45" s="11" t="n">
         <v>110</v>
       </c>
-      <c r="C45" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
         <is>
           <t>430→540</t>
         </is>
       </c>
-      <c r="F45" s="13" t="inlineStr">
+      <c r="G45" s="14" t="inlineStr">
         <is>
           <t>레이크머티리얼즈</t>
         </is>
       </c>
-      <c r="G45" s="14" t="n">
+      <c r="H45" s="15" t="n">
         <v>-43</v>
       </c>
-      <c r="H45" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I45" s="12" t="inlineStr">
+      <c r="I45" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J45" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="inlineStr">
         <is>
           <t>73→30</t>
         </is>
@@ -1692,30 +1913,40 @@
       <c r="B46" s="11" t="n">
         <v>108</v>
       </c>
-      <c r="C46" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
         <is>
           <t>547→655</t>
         </is>
       </c>
-      <c r="F46" s="13" t="inlineStr">
+      <c r="G46" s="14" t="inlineStr">
         <is>
           <t>에이프릴바이오  (편출)</t>
         </is>
       </c>
-      <c r="G46" s="14" t="n">
+      <c r="H46" s="15" t="n">
         <v>-40</v>
       </c>
-      <c r="H46" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I46" s="12" t="inlineStr">
+      <c r="I46" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J46" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
         <is>
           <t>40→0</t>
         </is>
@@ -1730,30 +1961,40 @@
       <c r="B47" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="C47" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D47" s="12" t="inlineStr">
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D47" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
         <is>
           <t>181→210</t>
         </is>
       </c>
-      <c r="F47" s="13" t="inlineStr">
+      <c r="G47" s="14" t="inlineStr">
         <is>
           <t>새로닉스</t>
         </is>
       </c>
-      <c r="G47" s="14" t="n">
+      <c r="H47" s="15" t="n">
         <v>-28</v>
       </c>
-      <c r="H47" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I47" s="12" t="inlineStr">
+      <c r="I47" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J47" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
         <is>
           <t>978→950</t>
         </is>
@@ -1768,30 +2009,40 @@
       <c r="B48" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="C48" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="12" t="inlineStr">
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
         <is>
           <t>58→85</t>
         </is>
       </c>
-      <c r="F48" s="13" t="inlineStr">
+      <c r="G48" s="14" t="inlineStr">
         <is>
           <t>덕산네오룩스</t>
         </is>
       </c>
-      <c r="G48" s="14" t="n">
+      <c r="H48" s="15" t="n">
         <v>-28</v>
       </c>
-      <c r="H48" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I48" s="12" t="inlineStr">
+      <c r="I48" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
         <is>
           <t>42→14</t>
         </is>
@@ -1806,30 +2057,40 @@
       <c r="B49" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="C49" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D49" s="12" t="inlineStr">
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D49" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
         <is>
           <t>587→612</t>
         </is>
       </c>
-      <c r="F49" s="13" t="inlineStr">
+      <c r="G49" s="14" t="inlineStr">
         <is>
           <t>씨젠</t>
         </is>
       </c>
-      <c r="G49" s="14" t="n">
+      <c r="H49" s="15" t="n">
         <v>-17</v>
       </c>
-      <c r="H49" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I49" s="12" t="inlineStr">
+      <c r="I49" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
         <is>
           <t>33→16</t>
         </is>
@@ -1844,30 +2105,40 @@
       <c r="B50" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="C50" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
         <is>
           <t>81→102</t>
         </is>
       </c>
-      <c r="F50" s="13" t="inlineStr">
+      <c r="G50" s="14" t="inlineStr">
         <is>
           <t>클래시스</t>
         </is>
       </c>
-      <c r="G50" s="14" t="n">
+      <c r="H50" s="15" t="n">
         <v>-17</v>
       </c>
-      <c r="H50" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I50" s="12" t="inlineStr">
+      <c r="I50" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J50" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
         <is>
           <t>73→56</t>
         </is>
@@ -1882,30 +2153,40 @@
       <c r="B51" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="C51" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D51" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
         <is>
           <t>60→77</t>
         </is>
       </c>
-      <c r="F51" s="13" t="inlineStr">
+      <c r="G51" s="14" t="inlineStr">
         <is>
           <t>실리콘투</t>
         </is>
       </c>
-      <c r="G51" s="14" t="n">
+      <c r="H51" s="15" t="n">
         <v>-15</v>
       </c>
-      <c r="H51" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I51" s="12" t="inlineStr">
+      <c r="I51" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J51" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="inlineStr">
         <is>
           <t>100→85</t>
         </is>
@@ -1920,30 +2201,40 @@
       <c r="B52" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="C52" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="12" t="inlineStr">
+      <c r="C52" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D52" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
         <is>
           <t>125→140</t>
         </is>
       </c>
-      <c r="F52" s="13" t="inlineStr">
+      <c r="G52" s="14" t="inlineStr">
         <is>
           <t>알지노믹스  (편출)</t>
         </is>
       </c>
-      <c r="G52" s="14" t="n">
+      <c r="H52" s="15" t="n">
         <v>-11</v>
       </c>
-      <c r="H52" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I52" s="12" t="inlineStr">
+      <c r="I52" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J52" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="inlineStr">
         <is>
           <t>11→0</t>
         </is>
@@ -1952,36 +2243,46 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>HK이노엔  (신규)</t>
+          <t>삼현</t>
         </is>
       </c>
       <c r="B53" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C53" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>0→11</t>
-        </is>
-      </c>
-      <c r="F53" s="13" t="inlineStr">
+      <c r="C53" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D53" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>29→40</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
         <is>
           <t>기가비스</t>
         </is>
       </c>
-      <c r="G53" s="14" t="n">
+      <c r="H53" s="15" t="n">
         <v>-11</v>
       </c>
-      <c r="H53" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I53" s="12" t="inlineStr">
+      <c r="I53" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J53" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="inlineStr">
         <is>
           <t>47→36</t>
         </is>
@@ -1990,112 +2291,142 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>삼현</t>
+          <t>HK이노엔  (신규)</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C54" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="12" t="inlineStr">
-        <is>
-          <t>29→40</t>
-        </is>
-      </c>
-      <c r="F54" s="13" t="inlineStr">
-        <is>
-          <t>파크시스템스</t>
-        </is>
-      </c>
-      <c r="G54" s="14" t="n">
+      <c r="C54" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D54" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>0→11</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="H54" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I54" s="12" t="inlineStr">
-        <is>
-          <t>41→32</t>
+      <c r="I54" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J54" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="inlineStr">
+        <is>
+          <t>116→107</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B55" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C55" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D55" s="12" t="inlineStr">
-        <is>
-          <t>60→68</t>
-        </is>
-      </c>
-      <c r="F55" s="13" t="inlineStr">
-        <is>
-          <t>피에스케이홀딩스</t>
-        </is>
-      </c>
-      <c r="G55" s="14" t="n">
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D55" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>52→60</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>파크시스템스</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="H55" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I55" s="12" t="inlineStr">
-        <is>
-          <t>116→107</t>
+      <c r="I55" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>41→32</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C56" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="12" t="inlineStr">
-        <is>
-          <t>52→60</t>
-        </is>
-      </c>
-      <c r="F56" s="13" t="inlineStr">
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D56" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>60→68</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
         <is>
           <t>리가켐바이오</t>
         </is>
       </c>
-      <c r="G56" s="14" t="n">
+      <c r="H56" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="H56" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I56" s="12" t="inlineStr">
+      <c r="I56" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
         <is>
           <t>13→7</t>
         </is>
@@ -2110,30 +2441,40 @@
       <c r="B57" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="C57" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="12" t="inlineStr">
+      <c r="C57" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D57" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
         <is>
           <t>39→46</t>
         </is>
       </c>
-      <c r="F57" s="13" t="inlineStr">
+      <c r="G57" s="14" t="inlineStr">
         <is>
           <t>코오롱티슈진</t>
         </is>
       </c>
-      <c r="G57" s="14" t="n">
+      <c r="H57" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="H57" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I57" s="12" t="inlineStr">
+      <c r="I57" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
         <is>
           <t>80→77</t>
         </is>
@@ -2148,20 +2489,26 @@
       <c r="B58" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C58" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="12" t="inlineStr">
+      <c r="C58" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D58" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
         <is>
           <t>0→4</t>
         </is>
       </c>
-      <c r="F58" s="15" t="n"/>
-      <c r="G58" s="15" t="n"/>
-      <c r="H58" s="15" t="n"/>
-      <c r="I58" s="15" t="n"/>
+      <c r="G58" s="17" t="n"/>
+      <c r="H58" s="17" t="n"/>
+      <c r="I58" s="17" t="n"/>
+      <c r="J58" s="17" t="n"/>
+      <c r="K58" s="17" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
@@ -2172,25 +2519,31 @@
       <c r="B59" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C59" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="12" t="inlineStr">
+      <c r="C59" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D59" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
         <is>
           <t>41→44</t>
         </is>
       </c>
-      <c r="F59" s="15" t="n"/>
-      <c r="G59" s="15" t="n"/>
-      <c r="H59" s="15" t="n"/>
-      <c r="I59" s="15" t="n"/>
+      <c r="G59" s="17" t="n"/>
+      <c r="H59" s="17" t="n"/>
+      <c r="I59" s="17" t="n"/>
+      <c r="J59" s="17" t="n"/>
+      <c r="K59" s="17" t="n"/>
     </row>
     <row r="61" ht="19" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      오늘 2026-07-01  vs  5일전 2026-06-24      매수 5종목  /  매도 4종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 613억      오늘 2026-07-01  vs  5일전 2026-06-24      매수 5종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B61" s="4" t="n"/>
@@ -2201,6 +2554,8 @@
       <c r="G61" s="4" t="n"/>
       <c r="H61" s="4" t="n"/>
       <c r="I61" s="4" t="n"/>
+      <c r="J61" s="4" t="n"/>
+      <c r="K61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -2211,14 +2566,16 @@
       <c r="B62" s="6" t="n"/>
       <c r="C62" s="6" t="n"/>
       <c r="D62" s="6" t="n"/>
-      <c r="F62" s="7" t="inlineStr">
+      <c r="E62" s="6" t="n"/>
+      <c r="G62" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="G62" s="8" t="n"/>
       <c r="H62" s="8" t="n"/>
       <c r="I62" s="8" t="n"/>
+      <c r="J62" s="8" t="n"/>
+      <c r="K62" s="8" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
@@ -2238,25 +2595,35 @@
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
+          <t>전체대비비중</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="F63" s="9" t="inlineStr">
+      <c r="G63" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G63" s="9" t="inlineStr">
+      <c r="H63" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="H63" s="9" t="inlineStr">
+      <c r="I63" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="I63" s="9" t="inlineStr">
+      <c r="J63" s="9" t="inlineStr">
+        <is>
+          <t>전체대비비중</t>
+        </is>
+      </c>
+      <c r="K63" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
@@ -2274,23 +2641,29 @@
       <c r="C64" s="11" t="n">
         <v>844928000</v>
       </c>
-      <c r="D64" s="12" t="inlineStr">
+      <c r="D64" s="12" t="n">
+        <v>1.379</v>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
         <is>
           <t>184→368</t>
         </is>
       </c>
-      <c r="F64" s="13" t="inlineStr">
+      <c r="G64" s="14" t="inlineStr">
         <is>
           <t>HLB이노베이션  (편출)</t>
         </is>
       </c>
-      <c r="G64" s="14" t="n">
+      <c r="H64" s="15" t="n">
         <v>-622</v>
       </c>
-      <c r="H64" s="14" t="n">
+      <c r="I64" s="15" t="n">
         <v>-849900800</v>
       </c>
-      <c r="I64" s="12" t="inlineStr">
+      <c r="J64" s="16" t="n">
+        <v>-1.387</v>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
         <is>
           <t>622→0</t>
         </is>
@@ -2308,23 +2681,29 @@
       <c r="C65" s="11" t="n">
         <v>431200000</v>
       </c>
-      <c r="D65" s="12" t="inlineStr">
+      <c r="D65" s="12" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
         <is>
           <t>354→398</t>
         </is>
       </c>
-      <c r="F65" s="13" t="inlineStr">
+      <c r="G65" s="14" t="inlineStr">
         <is>
           <t>에스바이오메딕스  (편출)</t>
         </is>
       </c>
-      <c r="G65" s="14" t="n">
+      <c r="H65" s="15" t="n">
         <v>-214</v>
       </c>
-      <c r="H65" s="14" t="n">
+      <c r="I65" s="15" t="n">
         <v>-486550400</v>
       </c>
-      <c r="I65" s="12" t="inlineStr">
+      <c r="J65" s="16" t="n">
+        <v>-0.794</v>
+      </c>
+      <c r="K65" s="13" t="inlineStr">
         <is>
           <t>214→0</t>
         </is>
@@ -2342,23 +2721,29 @@
       <c r="C66" s="11" t="n">
         <v>1300992000</v>
       </c>
-      <c r="D66" s="12" t="inlineStr">
+      <c r="D66" s="12" t="n">
+        <v>2.123</v>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
         <is>
           <t>0→32</t>
         </is>
       </c>
-      <c r="F66" s="13" t="inlineStr">
+      <c r="G66" s="14" t="inlineStr">
         <is>
           <t>지투지바이오  (편출)</t>
         </is>
       </c>
-      <c r="G66" s="14" t="n">
+      <c r="H66" s="15" t="n">
         <v>-136</v>
       </c>
-      <c r="H66" s="14" t="n">
+      <c r="I66" s="15" t="n">
         <v>-573484800</v>
       </c>
-      <c r="I66" s="12" t="inlineStr">
+      <c r="J66" s="16" t="n">
+        <v>-0.9360000000000001</v>
+      </c>
+      <c r="K66" s="13" t="inlineStr">
         <is>
           <t>136→0</t>
         </is>
@@ -2376,23 +2761,29 @@
       <c r="C67" s="11" t="n">
         <v>578760000</v>
       </c>
-      <c r="D67" s="12" t="inlineStr">
+      <c r="D67" s="12" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
         <is>
           <t>46→59</t>
         </is>
       </c>
-      <c r="F67" s="13" t="inlineStr">
+      <c r="G67" s="14" t="inlineStr">
         <is>
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="G67" s="14" t="n">
+      <c r="H67" s="15" t="n">
         <v>-17</v>
       </c>
-      <c r="H67" s="14" t="n">
+      <c r="I67" s="15" t="n">
         <v>-687344000</v>
       </c>
-      <c r="I67" s="12" t="inlineStr">
+      <c r="J67" s="16" t="n">
+        <v>-1.122</v>
+      </c>
+      <c r="K67" s="13" t="inlineStr">
         <is>
           <t>174→157</t>
         </is>
@@ -2410,54 +2801,60 @@
       <c r="C68" s="11" t="n">
         <v>185774400</v>
       </c>
-      <c r="D68" s="12" t="inlineStr">
+      <c r="D68" s="12" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="E68" s="13" t="inlineStr">
         <is>
           <t>53→62</t>
         </is>
       </c>
-      <c r="F68" s="15" t="n"/>
-      <c r="G68" s="15" t="n"/>
-      <c r="H68" s="15" t="n"/>
-      <c r="I68" s="15" t="n"/>
+      <c r="G68" s="17" t="n"/>
+      <c r="H68" s="17" t="n"/>
+      <c r="I68" s="17" t="n"/>
+      <c r="J68" s="17" t="n"/>
+      <c r="K68" s="17" t="n"/>
     </row>
     <row r="70" ht="19" customHeight="1">
-      <c r="A70" s="18" t="inlineStr">
+      <c r="A70" s="20" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B70" s="19" t="n"/>
-      <c r="C70" s="19" t="n"/>
-      <c r="D70" s="19" t="n"/>
-      <c r="E70" s="19" t="n"/>
-      <c r="F70" s="19" t="n"/>
-      <c r="G70" s="19" t="n"/>
-      <c r="H70" s="19" t="n"/>
-      <c r="I70" s="19" t="n"/>
+      <c r="B70" s="21" t="n"/>
+      <c r="C70" s="21" t="n"/>
+      <c r="D70" s="21" t="n"/>
+      <c r="E70" s="21" t="n"/>
+      <c r="F70" s="21" t="n"/>
+      <c r="G70" s="21" t="n"/>
+      <c r="H70" s="21" t="n"/>
+      <c r="I70" s="21" t="n"/>
+      <c r="J70" s="21" t="n"/>
+      <c r="K70" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A62:D62"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A40:I40"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="F36:I36"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="F41:I41"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="F62:I62"/>
-    <mergeCell ref="A70:I70"/>
-    <mergeCell ref="A61:I61"/>
+    <mergeCell ref="G36:K36"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A70:K70"/>
+    <mergeCell ref="A61:K61"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="G62:K62"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="G18:K18"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="G26:K26"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A35:K35"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="G41:K41"/>
+    <mergeCell ref="A40:K40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260701.xlsx
+++ b/reports/pdf_rolling5_20260701.xlsx
@@ -129,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -168,12 +168,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -865,21 +859,21 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2050422000</v>
+        <v>2607231000</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>0.355</v>
+        <v>0.451</v>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>28→43</t>
+          <t>25→40</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -905,21 +899,21 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2607231000</v>
+        <v>2050422000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>0.451</v>
+        <v>0.355</v>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>25→40</t>
+          <t>28→43</t>
         </is>
       </c>
       <c r="G12" s="17" t="n"/>
@@ -1769,15 +1763,11 @@
       <c r="B43" s="11" t="n">
         <v>175</v>
       </c>
-      <c r="C43" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C43" s="11" t="n">
+        <v>147651000</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>0.392</v>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
@@ -1792,15 +1782,11 @@
       <c r="H43" s="15" t="n">
         <v>-188</v>
       </c>
-      <c r="I43" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="15" t="n">
+        <v>-582941000</v>
+      </c>
+      <c r="J43" s="16" t="n">
+        <v>-1.549</v>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
@@ -1817,15 +1803,11 @@
       <c r="B44" s="11" t="n">
         <v>111</v>
       </c>
-      <c r="C44" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D44" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C44" s="11" t="n">
+        <v>30954570</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>0.082</v>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
@@ -1840,15 +1822,11 @@
       <c r="H44" s="15" t="n">
         <v>-50</v>
       </c>
-      <c r="I44" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J44" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I44" s="15" t="n">
+        <v>-79197500</v>
+      </c>
+      <c r="J44" s="16" t="n">
+        <v>-0.21</v>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
@@ -1865,15 +1843,11 @@
       <c r="B45" s="11" t="n">
         <v>110</v>
       </c>
-      <c r="C45" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D45" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C45" s="11" t="n">
+        <v>124962200</v>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>0.332</v>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
@@ -1888,15 +1862,11 @@
       <c r="H45" s="15" t="n">
         <v>-43</v>
       </c>
-      <c r="I45" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J45" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I45" s="15" t="n">
+        <v>-49324440</v>
+      </c>
+      <c r="J45" s="16" t="n">
+        <v>-0.131</v>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
@@ -1913,15 +1883,11 @@
       <c r="B46" s="11" t="n">
         <v>108</v>
       </c>
-      <c r="C46" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C46" s="11" t="n">
+        <v>447930000</v>
+      </c>
+      <c r="D46" s="12" t="n">
+        <v>1.19</v>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
@@ -1936,15 +1902,11 @@
       <c r="H46" s="15" t="n">
         <v>-40</v>
       </c>
-      <c r="I46" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J46" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I46" s="15" t="n">
+        <v>-128138000</v>
+      </c>
+      <c r="J46" s="16" t="n">
+        <v>-0.34</v>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
@@ -1961,15 +1923,11 @@
       <c r="B47" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="C47" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D47" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C47" s="11" t="n">
+        <v>107677000</v>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>0.286</v>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
@@ -1984,15 +1942,11 @@
       <c r="H47" s="15" t="n">
         <v>-28</v>
       </c>
-      <c r="I47" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J47" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I47" s="15" t="n">
+        <v>-24619560</v>
+      </c>
+      <c r="J47" s="16" t="n">
+        <v>-0.065</v>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
@@ -2009,15 +1963,11 @@
       <c r="B48" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="C48" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C48" s="11" t="n">
+        <v>47565900</v>
+      </c>
+      <c r="D48" s="12" t="n">
+        <v>0.126</v>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
@@ -2032,15 +1982,11 @@
       <c r="H48" s="15" t="n">
         <v>-28</v>
       </c>
-      <c r="I48" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J48" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I48" s="15" t="n">
+        <v>-72553600</v>
+      </c>
+      <c r="J48" s="16" t="n">
+        <v>-0.193</v>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
@@ -2057,15 +2003,11 @@
       <c r="B49" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="C49" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D49" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C49" s="11" t="n">
+        <v>46116250</v>
+      </c>
+      <c r="D49" s="12" t="n">
+        <v>0.123</v>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
@@ -2074,25 +2016,21 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>클래시스</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-17</v>
       </c>
-      <c r="I49" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J49" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I49" s="15" t="n">
+        <v>-62583800</v>
+      </c>
+      <c r="J49" s="16" t="n">
+        <v>-0.166</v>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>33→16</t>
+          <t>73→56</t>
         </is>
       </c>
     </row>
@@ -2105,15 +2043,11 @@
       <c r="B50" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="C50" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C50" s="11" t="n">
+        <v>85604400</v>
+      </c>
+      <c r="D50" s="12" t="n">
+        <v>0.227</v>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
@@ -2122,25 +2056,21 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>클래시스</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-17</v>
       </c>
-      <c r="I50" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J50" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I50" s="15" t="n">
+        <v>-39887100</v>
+      </c>
+      <c r="J50" s="16" t="n">
+        <v>-0.106</v>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>73→56</t>
+          <t>33→16</t>
         </is>
       </c>
     </row>
@@ -2153,15 +2083,11 @@
       <c r="B51" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="C51" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C51" s="11" t="n">
+        <v>39819950</v>
+      </c>
+      <c r="D51" s="12" t="n">
+        <v>0.106</v>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
@@ -2176,15 +2102,11 @@
       <c r="H51" s="15" t="n">
         <v>-15</v>
       </c>
-      <c r="I51" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J51" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I51" s="15" t="n">
+        <v>-37505250</v>
+      </c>
+      <c r="J51" s="16" t="n">
+        <v>-0.1</v>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
@@ -2201,15 +2123,11 @@
       <c r="B52" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="C52" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C52" s="11" t="n">
+        <v>98236500</v>
+      </c>
+      <c r="D52" s="12" t="n">
+        <v>0.261</v>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
@@ -2224,15 +2142,11 @@
       <c r="H52" s="15" t="n">
         <v>-11</v>
       </c>
-      <c r="I52" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J52" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I52" s="15" t="n">
+        <v>-35629000</v>
+      </c>
+      <c r="J52" s="16" t="n">
+        <v>-0.095</v>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
@@ -2243,25 +2157,21 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>삼현</t>
+          <t>HK이노엔  (신규)</t>
         </is>
       </c>
       <c r="B53" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C53" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C53" s="11" t="n">
+        <v>35194500</v>
+      </c>
+      <c r="D53" s="12" t="n">
+        <v>0.093</v>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>29→40</t>
+          <t>0→11</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
@@ -2272,15 +2182,11 @@
       <c r="H53" s="15" t="n">
         <v>-11</v>
       </c>
-      <c r="I53" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J53" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I53" s="15" t="n">
+        <v>-167021800</v>
+      </c>
+      <c r="J53" s="16" t="n">
+        <v>-0.444</v>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
@@ -2291,25 +2197,21 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>HK이노엔  (신규)</t>
+          <t>삼현</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C54" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C54" s="11" t="n">
+        <v>30154300</v>
+      </c>
+      <c r="D54" s="12" t="n">
+        <v>0.08</v>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>0→11</t>
+          <t>29→40</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -2320,15 +2222,11 @@
       <c r="H54" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="I54" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J54" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I54" s="15" t="n">
+        <v>-113760000</v>
+      </c>
+      <c r="J54" s="16" t="n">
+        <v>-0.302</v>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
@@ -2345,15 +2243,11 @@
       <c r="B55" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C55" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D55" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C55" s="11" t="n">
+        <v>123935200</v>
+      </c>
+      <c r="D55" s="12" t="n">
+        <v>0.329</v>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
@@ -2368,15 +2262,11 @@
       <c r="H55" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="I55" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I55" s="15" t="n">
+        <v>-176683500</v>
+      </c>
+      <c r="J55" s="16" t="n">
+        <v>-0.469</v>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
@@ -2393,15 +2283,11 @@
       <c r="B56" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C56" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C56" s="11" t="n">
+        <v>106239200</v>
+      </c>
+      <c r="D56" s="12" t="n">
+        <v>0.282</v>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
@@ -2416,15 +2302,11 @@
       <c r="H56" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I56" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J56" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I56" s="15" t="n">
+        <v>-71052600</v>
+      </c>
+      <c r="J56" s="16" t="n">
+        <v>-0.189</v>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
@@ -2441,15 +2323,11 @@
       <c r="B57" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="C57" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C57" s="11" t="n">
+        <v>51594900</v>
+      </c>
+      <c r="D57" s="12" t="n">
+        <v>0.137</v>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
@@ -2464,15 +2342,11 @@
       <c r="H57" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I57" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I57" s="15" t="n">
+        <v>-22183200</v>
+      </c>
+      <c r="J57" s="16" t="n">
+        <v>-0.059</v>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
@@ -2489,15 +2363,11 @@
       <c r="B58" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C58" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C58" s="11" t="n">
+        <v>114708000</v>
+      </c>
+      <c r="D58" s="12" t="n">
+        <v>0.305</v>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
@@ -2519,15 +2389,11 @@
       <c r="B59" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C59" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C59" s="11" t="n">
+        <v>64582500</v>
+      </c>
+      <c r="D59" s="12" t="n">
+        <v>0.172</v>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
@@ -2816,21 +2682,21 @@
       <c r="K68" s="17" t="n"/>
     </row>
     <row r="70" ht="19" customHeight="1">
-      <c r="A70" s="20" t="inlineStr">
+      <c r="A70" s="18" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B70" s="21" t="n"/>
-      <c r="C70" s="21" t="n"/>
-      <c r="D70" s="21" t="n"/>
-      <c r="E70" s="21" t="n"/>
-      <c r="F70" s="21" t="n"/>
-      <c r="G70" s="21" t="n"/>
-      <c r="H70" s="21" t="n"/>
-      <c r="I70" s="21" t="n"/>
-      <c r="J70" s="21" t="n"/>
-      <c r="K70" s="21" t="n"/>
+      <c r="B70" s="19" t="n"/>
+      <c r="C70" s="19" t="n"/>
+      <c r="D70" s="19" t="n"/>
+      <c r="E70" s="19" t="n"/>
+      <c r="F70" s="19" t="n"/>
+      <c r="G70" s="19" t="n"/>
+      <c r="H70" s="19" t="n"/>
+      <c r="I70" s="19" t="n"/>
+      <c r="J70" s="19" t="n"/>
+      <c r="K70" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="21">

--- a/reports/pdf_rolling5_20260701.xlsx
+++ b/reports/pdf_rolling5_20260701.xlsx
@@ -859,21 +859,21 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2607231000</v>
+        <v>2050422000</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>0.451</v>
+        <v>0.355</v>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>25→40</t>
+          <t>28→43</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -899,21 +899,21 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2050422000</v>
+        <v>2607231000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>0.355</v>
+        <v>0.451</v>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>28→43</t>
+          <t>25→40</t>
         </is>
       </c>
       <c r="G12" s="17" t="n"/>
@@ -1447,21 +1447,21 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="B31" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>1306594800</v>
+        <v>2470305600</v>
       </c>
       <c r="D31" s="12" t="n">
-        <v>0.358</v>
+        <v>0.677</v>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>99→120</t>
+          <t>19→40</t>
         </is>
       </c>
       <c r="G31" s="14" t="inlineStr">
@@ -1487,21 +1487,21 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B32" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2470305600</v>
+        <v>1306594800</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>0.677</v>
+        <v>0.358</v>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>19→40</t>
+          <t>99→120</t>
         </is>
       </c>
       <c r="G32" s="17" t="n"/>
@@ -1936,21 +1936,21 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>새로닉스</t>
+          <t>덕산네오룩스</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-28</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-24619560</v>
+        <v>-72553600</v>
       </c>
       <c r="J47" s="16" t="n">
-        <v>-0.065</v>
+        <v>-0.193</v>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>978→950</t>
+          <t>42→14</t>
         </is>
       </c>
     </row>
@@ -1976,21 +1976,21 @@
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>덕산네오룩스</t>
+          <t>새로닉스</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
         <v>-28</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-72553600</v>
+        <v>-24619560</v>
       </c>
       <c r="J48" s="16" t="n">
-        <v>-0.193</v>
+        <v>-0.065</v>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>42→14</t>
+          <t>978→950</t>
         </is>
       </c>
     </row>
@@ -2016,21 +2016,21 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>클래시스</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-17</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-62583800</v>
+        <v>-39887100</v>
       </c>
       <c r="J49" s="16" t="n">
-        <v>-0.166</v>
+        <v>-0.106</v>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>73→56</t>
+          <t>33→16</t>
         </is>
       </c>
     </row>
@@ -2056,21 +2056,21 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>클래시스</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-17</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-39887100</v>
+        <v>-62583800</v>
       </c>
       <c r="J50" s="16" t="n">
-        <v>-0.106</v>
+        <v>-0.166</v>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>33→16</t>
+          <t>73→56</t>
         </is>
       </c>
     </row>
@@ -2157,21 +2157,21 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>HK이노엔  (신규)</t>
+          <t>삼현</t>
         </is>
       </c>
       <c r="B53" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>35194500</v>
+        <v>30154300</v>
       </c>
       <c r="D53" s="12" t="n">
-        <v>0.093</v>
+        <v>0.08</v>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>0→11</t>
+          <t>29→40</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
@@ -2197,40 +2197,40 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>삼현</t>
+          <t>HK이노엔  (신규)</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>30154300</v>
+        <v>35194500</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>0.08</v>
+        <v>0.093</v>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>29→40</t>
+          <t>0→11</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-113760000</v>
+        <v>-176683500</v>
       </c>
       <c r="J54" s="16" t="n">
-        <v>-0.302</v>
+        <v>-0.469</v>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>116→107</t>
+          <t>41→32</t>
         </is>
       </c>
     </row>
@@ -2256,21 +2256,21 @@
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-176683500</v>
+        <v>-113760000</v>
       </c>
       <c r="J55" s="16" t="n">
-        <v>-0.469</v>
+        <v>-0.302</v>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>41→32</t>
+          <t>116→107</t>
         </is>
       </c>
     </row>
